--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487695_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487695_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1934</v>
+        <v>4.1394</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7117</v>
+        <v>2.012</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4817</v>
+        <v>2.1274</v>
       </c>
       <c r="G2" t="n">
         <v>2.9864</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2966</v>
+        <v>0.2425</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0863</v>
+        <v>0.3866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2102</v>
+        <v>-0.1441</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1307</v>
+        <v>3.3125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8189</v>
+        <v>0.919</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3117</v>
+        <v>2.3935</v>
       </c>
       <c r="G3" t="n">
         <v>0.3846</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.042</v>
+        <v>0.1399</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0348</v>
+        <v>0.0653</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0072</v>
+        <v>0.0746</v>
       </c>
       <c r="V3" t="n">
         <v>2.4</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9881</v>
+        <v>1.1422</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8557</v>
+        <v>1.2551</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1324</v>
+        <v>-0.1129</v>
       </c>
       <c r="G4" t="n">
         <v>1.0703</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1999</v>
+        <v>-0.646</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.2013</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.602</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.3299</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2541</v>
+        <v>-0.2466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2284</v>
+        <v>-1.5088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0257</v>
+        <v>1.2622</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7165</v>
+        <v>-0.0358</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2037</v>
+        <v>0.7472</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4872</v>
+        <v>-0.783</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6823</v>
+        <v>0.3231</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3141</v>
+        <v>1.4953</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6318</v>
+        <v>-1.1723</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0342</v>
+        <v>-0.3588</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104</v>
+        <v>-0.7481</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1446</v>
+        <v>0.3893</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004</v>
+        <v>0.519</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9107</v>
+        <v>0.3025</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9103</v>
+        <v>0.2165</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.292</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4087</v>
+        <v>-0.3722</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4802</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0358</v>
+        <v>-0.7165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7472</v>
+        <v>-1.2037</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.783</v>
+        <v>0.4872</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3231</v>
+        <v>-0.6823</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4953</v>
+        <v>-1.3141</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1723</v>
+        <v>0.6318</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3588</v>
+        <v>-0.0342</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7481</v>
+        <v>0.1104</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3893</v>
+        <v>-0.1446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9105</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8371</v>
+        <v>-0.5456</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4026</v>
+        <v>0.3101</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4345</v>
+        <v>-0.8557</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5003</v>
+        <v>-1.1182</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2009</v>
+        <v>0.5012</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7011</v>
+        <v>-1.6194</v>
       </c>
       <c r="G7" t="n">
         <v>1.7296</v>
@@ -1000,13 +1000,13 @@
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.2061</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1088</v>
+        <v>0.1915</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4794</v>
+        <v>-0.3976</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4477</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1664</v>
+        <v>-1.5752</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8167</v>
+        <v>-3.4163</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6502</v>
+        <v>1.841</v>
       </c>
       <c r="G8" t="n">
         <v>0.9822</v>
@@ -1078,13 +1078,13 @@
         <v>3.1045</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6725</v>
+        <v>-0.0813</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2042</v>
+        <v>0.1962</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4683</v>
+        <v>-0.2776</v>
       </c>
       <c r="V8" t="n">
         <v>-1.506</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8632</v>
+        <v>-2.554</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7146</v>
+        <v>-2.5144</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1486</v>
+        <v>-0.0396</v>
       </c>
       <c r="G9" t="n">
         <v>0.1335</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.2125</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1951</v>
+        <v>0.3953</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2918</v>
+        <v>-0.1828</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3776</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3899</v>
+        <v>-3.1964</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8852</v>
+        <v>-2.995</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5047</v>
+        <v>-0.2014</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7486</v>
+        <v>-1.4832</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6875</v>
+        <v>-0.4622</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0611</v>
+        <v>-1.021</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3833</v>
+        <v>-0.9705</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8784</v>
+        <v>-0.3666</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5049</v>
+        <v>-0.6039</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3652</v>
+        <v>-0.5127</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8091</v>
+        <v>-0.0956</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5561</v>
+        <v>-0.4171</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.9702</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.1344</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.6115</v>
+        <v>-0.743</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4385</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.05</v>
+        <v>-0.6589</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.406</v>
+        <v>-3.3448</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3954</v>
+        <v>-2.0854</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0106</v>
+        <v>-1.2594</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4832</v>
+        <v>-3.7486</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4622</v>
+        <v>-2.6875</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.021</v>
+        <v>-1.0611</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9705</v>
+        <v>-2.3833</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3666</v>
+        <v>-1.8784</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6039</v>
+        <v>-0.5049</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5127</v>
+        <v>-1.3652</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0956</v>
+        <v>-0.8091</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4171</v>
+        <v>-0.5561</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9702</v>
+        <v>0.9702</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9527</v>
+        <v>-0.5664</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4845</v>
+        <v>0.2383</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4681</v>
+        <v>-0.8047</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9654</v>
+        <v>-4.9203</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.163</v>
+        <v>-4.3632</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8024</v>
+        <v>-0.5571</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9719</v>
@@ -1390,13 +1390,13 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1577</v>
+        <v>-1.1126</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1077</v>
+        <v>-0.3079</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.05</v>
+        <v>-0.8047</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8358</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.6534</v>
+        <v>-8.653400000000001</v>
       </c>
       <c r="E13" t="n">
         <v>-12.568</v>
@@ -1435,10 +1435,10 @@
         <v>-0.6694000000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.05790000000000017</v>
+        <v>-0.05789999999999995</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6114999999999999</v>
+        <v>-0.6114999999999997</v>
       </c>
       <c r="J13" t="n">
         <v>-0.706</v>
@@ -1450,7 +1450,7 @@
         <v>-1.8349</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03659999999999985</v>
+        <v>0.03659999999999974</v>
       </c>
       <c r="N13" t="n">
         <v>-1.1866</v>
@@ -1459,7 +1459,7 @@
         <v>1.2234</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9702999999999995</v>
+        <v>0.9702999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.4033</v>
@@ -1468,13 +1468,13 @@
         <v>20.3736</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7873</v>
+        <v>-2.7871</v>
       </c>
       <c r="T13" t="n">
         <v>1.8951</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.6824</v>
+        <v>-4.6823</v>
       </c>
       <c r="V13" t="n">
         <v>-6.1671</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1211</v>
+        <v>9.238099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3064</v>
+        <v>7.8049</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8147</v>
+        <v>1.4331</v>
       </c>
       <c r="G14" t="n">
         <v>5.5271</v>
@@ -1546,13 +1546,13 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9656</v>
+        <v>1.0826</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5134</v>
+        <v>1.0119</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5477</v>
+        <v>0.0707</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2821</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1183</v>
+        <v>1.9256</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6322</v>
+        <v>-0.9273</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7505</v>
+        <v>2.8529</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1501</v>
+        <v>-0.6607</v>
       </c>
       <c r="H15" t="n">
-        <v>1.09</v>
+        <v>-0.0634</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9398</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9268</v>
+        <v>-1.1931</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0752</v>
+        <v>-0.4902</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.002</v>
+        <v>-0.7029</v>
       </c>
       <c r="M15" t="n">
-        <v>1.077</v>
+        <v>0.5324</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0148</v>
+        <v>0.4267</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0622</v>
+        <v>0.1056</v>
       </c>
       <c r="P15" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>2.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7741</v>
+        <v>0.9281</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0471</v>
+        <v>0.9539</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8213</v>
+        <v>-0.0258</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W15" t="n">
         <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9134</v>
+        <v>1.8684</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1275</v>
+        <v>-2.0316</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0409</v>
+        <v>3.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6607</v>
+        <v>0.1501</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0634</v>
+        <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.9398</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1931</v>
+        <v>-0.9268</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4902</v>
+        <v>1.0752</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7029</v>
+        <v>-2.002</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5324</v>
+        <v>1.077</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4267</v>
+        <v>0.0148</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1056</v>
+        <v>1.0622</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9105</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.08409999999999999</v>
+        <v>1.5242</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7537</v>
+        <v>0.5535</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8378</v>
+        <v>0.9708</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0.2821</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ALIK</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6653</v>
+        <v>1.7836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2092</v>
+        <v>-2.0495</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4561</v>
+        <v>3.8331</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3925</v>
+        <v>0.3291</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0601</v>
+        <v>-0.4128</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4527</v>
+        <v>0.7419</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6937</v>
+        <v>0.0318</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0371</v>
+        <v>0.2019</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7307</v>
+        <v>-0.1701</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3011</v>
+        <v>0.2973</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0231</v>
+        <v>-0.6146</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2781</v>
+        <v>0.912</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-4.4627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-7.7613</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>3.2985</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2728</v>
+        <v>1.0218</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4856</v>
+        <v>0.7845</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2129</v>
+        <v>0.2373</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.8955</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.8955</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>J. ALIK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.246</v>
+        <v>0.4924</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0505</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2965</v>
+        <v>0.4834</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3291</v>
+        <v>0.3925</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4128</v>
+        <v>-0.0601</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7419</v>
+        <v>0.4527</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0318</v>
+        <v>0.6937</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2019</v>
+        <v>-0.0371</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1701</v>
+        <v>0.7307</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2973</v>
+        <v>-0.3011</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6146</v>
+        <v>-0.0231</v>
       </c>
       <c r="O18" t="n">
-        <v>0.912</v>
+        <v>-0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.4627</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.7613</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2985</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5159</v>
+        <v>0.0998</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2165</v>
+        <v>0.2854</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2994</v>
+        <v>-0.1856</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8955</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.8955</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5131</v>
+        <v>-0.1311</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0618</v>
+        <v>0.3621</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5749</v>
+        <v>-0.4932</v>
       </c>
       <c r="G19" t="n">
         <v>0.1172</v>
@@ -1936,13 +1936,13 @@
         <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2124</v>
+        <v>0.1696</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.3003</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6119</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAWARA</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7453</v>
+        <v>-1.0829</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6505</v>
+        <v>-1.8516</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9052</v>
+        <v>0.7687</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4258</v>
+        <v>0.6278</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4213</v>
+        <v>1.0043</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0045</v>
+        <v>-0.3765</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7778</v>
+        <v>0.4731</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9402</v>
+        <v>0.4325</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1624</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6481</v>
+        <v>0.1546</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4812</v>
+        <v>0.5718</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1669</v>
+        <v>-0.4171</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1045</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7402</v>
+        <v>-0.8465</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7855</v>
+        <v>-0.3844</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0453</v>
+        <v>-0.4621</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>M. DIAWARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.183</v>
+        <v>-1.3698</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9517</v>
+        <v>-2.3512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7687</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6278</v>
+        <v>-2.4258</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0043</v>
+        <v>-2.4213</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3765</v>
+        <v>-0.0045</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4731</v>
+        <v>-1.7778</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4325</v>
+        <v>-1.9402</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0406</v>
+        <v>0.1624</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1546</v>
+        <v>-0.6481</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5718</v>
+        <v>-0.4812</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4171</v>
+        <v>-0.1669</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3582</v>
+        <v>3.1045</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9466</v>
+        <v>1.1157</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4845</v>
+        <v>1.0848</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4621</v>
+        <v>0.0309</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9692</v>
+        <v>-2.0688</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0793</v>
+        <v>-2.8791</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1101</v>
+        <v>0.8103</v>
       </c>
       <c r="G22" t="n">
         <v>-3.388</v>
@@ -2170,13 +2170,13 @@
         <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2066</v>
+        <v>-0.3062</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1077</v>
+        <v>0.0925</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0989</v>
+        <v>-0.3987</v>
       </c>
       <c r="V22" t="n">
         <v>3.9537</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.653499999999998</v>
+        <v>10.6555</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.914299999999999</v>
+        <v>-3.9143</v>
       </c>
       <c r="F23" t="n">
-        <v>12.5678</v>
+        <v>14.5697</v>
       </c>
       <c r="G23" t="n">
         <v>0.6692999999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05779999999999985</v>
+        <v>0.05779999999999896</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6117</v>
+        <v>0.6117000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>-0.03669999999999973</v>
@@ -2230,7 +2230,7 @@
         <v>-1.2233</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7059999999999997</v>
+        <v>0.7059999999999995</v>
       </c>
       <c r="N23" t="n">
         <v>-1.1289</v>
@@ -2248,13 +2248,13 @@
         <v>19.4032</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7871</v>
+        <v>4.789099999999999</v>
       </c>
       <c r="T23" t="n">
         <v>4.6824</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8952</v>
+        <v>0.1067999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>6.1671</v>
